--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487140_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487140_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8745</v>
+        <v>1.2192</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8884</v>
+        <v>1.4472</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0138</v>
+        <v>-0.228</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4048</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1792</v>
+        <v>0.5238</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5764</v>
+        <v>0.1352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6028</v>
+        <v>0.3886</v>
       </c>
       <c r="V2" t="n">
         <v>0.3281</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8547</v>
+        <v>-0.2432</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5621</v>
+        <v>-0.5648</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7074</v>
+        <v>0.3216</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.9007</v>
+        <v>-0.7782</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1128</v>
+        <v>-0.679</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0135</v>
+        <v>-0.0993</v>
       </c>
       <c r="J3" t="n">
-        <v>1.743</v>
+        <v>-0.5648</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7023</v>
+        <v>-0.6055</v>
       </c>
       <c r="L3" t="n">
         <v>0.0407</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.6438</v>
+        <v>-0.2134</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5895</v>
+        <v>-0.0735</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0542</v>
+        <v>-0.14</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6625</v>
+        <v>0.149</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9494</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>X. OSTOLAZA OSTOLAZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1153</v>
+        <v>-0.4335</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6243</v>
+        <v>-0.1697</v>
       </c>
       <c r="F4" t="n">
-        <v>0.509</v>
+        <v>-0.2638</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7782</v>
+        <v>0.0007</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.679</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0993</v>
+        <v>-0.0293</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5648</v>
+        <v>0.7547</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6055</v>
+        <v>0.1035</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0407</v>
+        <v>0.6512</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2134</v>
+        <v>-0.7539</v>
       </c>
       <c r="N4" t="n">
         <v>-0.0735</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.14</v>
+        <v>-0.6805</v>
       </c>
       <c r="P4" t="n">
-        <v>0.386</v>
+        <v>-0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>0.386</v>
+        <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2769</v>
+        <v>-0.0483</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3364</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. OSTOLAZA OSTOLAZA</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5604</v>
+        <v>-0.4832</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2698</v>
+        <v>2.5186</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2906</v>
+        <v>-3.0018</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0007</v>
+        <v>-1.9007</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>0.1128</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0293</v>
+        <v>-2.0135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7547</v>
+        <v>1.743</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1035</v>
+        <v>1.7023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6512</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7539</v>
+        <v>-3.6438</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0735</v>
+        <v>-1.5895</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6805</v>
+        <v>-2.0542</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1752</v>
+        <v>1.3246</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0595</v>
+        <v>0.9059</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1157</v>
+        <v>0.4187</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0426</v>
+        <v>-1.1428</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3129</v>
+        <v>-0.4131</v>
       </c>
       <c r="F6" t="n">
         <v>-0.7297</v>
@@ -922,10 +922,10 @@
         <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5341</v>
+        <v>0.4339</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3107</v>
+        <v>0.2105</v>
       </c>
       <c r="U6" t="n">
         <v>0.2234</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6242</v>
+        <v>-1.6659</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8868</v>
+        <v>1.2467</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.511</v>
+        <v>-2.9125</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3417</v>
@@ -1000,13 +1000,13 @@
         <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4316</v>
+        <v>0.39</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2102</v>
+        <v>0.1497</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6418</v>
+        <v>0.2402</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9421</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7057</v>
+        <v>-2.1712</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7538</v>
+        <v>-2.3532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0481</v>
+        <v>0.182</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0714</v>
@@ -1078,13 +1078,13 @@
         <v>0.772</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4303</v>
+        <v>0.1041</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1785</v>
+        <v>0.2221</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2518</v>
+        <v>-0.118</v>
       </c>
       <c r="V8" t="n">
         <v>1.8842</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3029</v>
+        <v>-2.4879</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.577</v>
+        <v>-1.9762</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7259</v>
+        <v>-0.5118</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0002</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6888</v>
+        <v>0.1262</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6544</v>
+        <v>-0.0535</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0344</v>
+        <v>0.1798</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3892</v>
+        <v>-3.0478</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5954</v>
+        <v>-1.5752</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7938</v>
+        <v>-1.4726</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9199</v>
@@ -1234,13 +1234,13 @@
         <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8552999999999999</v>
+        <v>0.4862</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2492</v>
+        <v>-0.229</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3939</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-0.614</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7828</v>
+        <v>-5.6767</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6203</v>
+        <v>-4.7016</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1625</v>
+        <v>-0.9751</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5251</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3166</v>
+        <v>0.4227</v>
       </c>
       <c r="T11" t="n">
-        <v>0.041</v>
+        <v>-0.0403</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2756</v>
+        <v>0.463</v>
       </c>
       <c r="V11" t="n">
         <v>1.5138</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.9779</v>
+        <v>-8.044</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.1737</v>
+        <v>-6.4539</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8042</v>
+        <v>-1.5901</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8108</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9862</v>
+        <v>-0.0522</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8183</v>
+        <v>-0.0985</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1679</v>
+        <v>0.0462</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2859</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.7718</v>
+        <v>-24.177</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.5899</v>
+        <v>-12.9952</v>
       </c>
       <c r="F13" t="n">
         <v>-11.1818</v>
@@ -1468,13 +1468,13 @@
         <v>12.5455</v>
       </c>
       <c r="S13" t="n">
-        <v>3.265100000000001</v>
+        <v>3.86</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6478999999999993</v>
+        <v>1.2428</v>
       </c>
       <c r="U13" t="n">
-        <v>2.617299999999999</v>
+        <v>2.6172</v>
       </c>
       <c r="V13" t="n">
         <v>1.5983</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9923</v>
+        <v>6.9989</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1123</v>
+        <v>5.0122</v>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>1.9868</v>
       </c>
       <c r="G14" t="n">
         <v>2.9147</v>
@@ -1546,13 +1546,13 @@
         <v>2.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1514</v>
+        <v>-0.1448</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1507</v>
+        <v>-0.2508</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0007</v>
+        <v>0.1061</v>
       </c>
       <c r="V14" t="n">
         <v>1.3339</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7985</v>
+        <v>5.7859</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4886</v>
+        <v>1.9661</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3099</v>
+        <v>3.8198</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9483</v>
+        <v>5.7188</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4571</v>
+        <v>2.1973</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4912</v>
+        <v>3.5215</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2342</v>
+        <v>5.1382</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3388</v>
+        <v>3.0789</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8954</v>
+        <v>2.0592</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.5806</v>
       </c>
       <c r="N15" t="n">
         <v>-0.8817</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5958</v>
+        <v>1.4623</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>3.4741</v>
+        <v>3.2811</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8778</v>
+        <v>-0.3189</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1845</v>
+        <v>-0.2769</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6933</v>
+        <v>-0.042</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8642</v>
+        <v>5.5799</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3653</v>
+        <v>4.5255</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4989</v>
+        <v>1.0544</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7188</v>
+        <v>4.8006</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1973</v>
+        <v>-0.5703</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5215</v>
+        <v>5.3709</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1382</v>
+        <v>5.6485</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0789</v>
+        <v>1.0659</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0592</v>
+        <v>4.5826</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5806</v>
+        <v>-0.8479</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8817</v>
+        <v>-1.6361</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4623</v>
+        <v>0.7883</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2811</v>
+        <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2407</v>
+        <v>-0.5718</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8778</v>
+        <v>-0.158</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3629</v>
+        <v>-0.4138</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5243</v>
+        <v>5.4151</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9247</v>
+        <v>1.5874</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5997</v>
+        <v>3.8277</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8006</v>
+        <v>3.9483</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5703</v>
+        <v>1.4571</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3709</v>
+        <v>2.4912</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6485</v>
+        <v>3.2342</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0659</v>
+        <v>2.3388</v>
       </c>
       <c r="L17" t="n">
-        <v>4.5826</v>
+        <v>0.8954</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8479</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6361</v>
+        <v>-0.8817</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7883</v>
+        <v>1.5958</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3161</v>
+        <v>3.4741</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6273</v>
+        <v>0.4944</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7588</v>
+        <v>0.2833</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8686</v>
+        <v>0.2111</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7811</v>
+        <v>3.554</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1996</v>
+        <v>1.9993</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5814</v>
+        <v>1.5547</v>
       </c>
       <c r="G18" t="n">
         <v>0.4405</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5374</v>
+        <v>-0.7644</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4627</v>
+        <v>-0.6629</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0747</v>
+        <v>-0.1015</v>
       </c>
       <c r="V18" t="n">
         <v>1.9478</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6162</v>
+        <v>2.6766</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5962</v>
+        <v>1.4961</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0199</v>
+        <v>1.1805</v>
       </c>
       <c r="G19" t="n">
         <v>1.5337</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5023</v>
+        <v>-0.4419</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1652</v>
+        <v>-0.2654</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3371</v>
+        <v>-0.1765</v>
       </c>
       <c r="V19" t="n">
         <v>1.0058</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3143</v>
+        <v>1.1606</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5942</v>
+        <v>-1.6944</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9085</v>
+        <v>2.8549</v>
       </c>
       <c r="G20" t="n">
         <v>1.3677</v>
@@ -2014,13 +2014,13 @@
         <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2168</v>
+        <v>0.0631</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0251</v>
+        <v>-0.0284</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6562</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5799</v>
+        <v>0.76</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6524</v>
+        <v>1.7525</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0725</v>
+        <v>-0.9925</v>
       </c>
       <c r="G21" t="n">
         <v>0.53</v>
@@ -2092,13 +2092,13 @@
         <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1428</v>
+        <v>0.3229</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0145</v>
+        <v>0.1147</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1282</v>
+        <v>0.2082</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2859</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0505</v>
+        <v>0.4978</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9049</v>
+        <v>-1.7046</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8544</v>
+        <v>2.2024</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8587</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1349</v>
+        <v>-0.5866</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8328</v>
+        <v>-0.6325</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3021</v>
+        <v>0.0459</v>
       </c>
       <c r="V22" t="n">
         <v>-0.18</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6349</v>
+        <v>-2.4882</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1949</v>
+        <v>-0.9947</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.44</v>
+        <v>-1.4935</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7312</v>
@@ -2248,13 +2248,13 @@
         <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6888</v>
+        <v>-0.542</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7139</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0251</v>
+        <v>-0.0284</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4079</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0135</v>
+        <v>-4.5013</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4634</v>
+        <v>-2.7638</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5501</v>
+        <v>-1.7374</v>
       </c>
       <c r="G24" t="n">
         <v>0.3206</v>
@@ -2326,13 +2326,13 @@
         <v>0.965</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3801</v>
+        <v>-0.1077</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0462</v>
+        <v>-0.3467</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4263</v>
+        <v>0.2389</v>
       </c>
       <c r="V24" t="n">
         <v>-2.784</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>24.7719</v>
+        <v>25.4393</v>
       </c>
       <c r="E25" t="n">
-        <v>11.1817</v>
+        <v>11.1816</v>
       </c>
       <c r="F25" t="n">
-        <v>13.5901</v>
+        <v>14.2578</v>
       </c>
       <c r="G25" t="n">
         <v>19.985</v>
@@ -2404,13 +2404,13 @@
         <v>22.1958</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.2653</v>
+        <v>-2.5977</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6174</v>
+        <v>-2.6172</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6481</v>
+        <v>0.01959999999999995</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5982</v>
